--- a/results/Int All Data 0.5/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.5/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>-0.0002868253273004107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008532057430597973</v>
+        <v>0.0008584550868918174</v>
       </c>
       <c r="F3" t="n">
         <v>0.0002965760573642439</v>
@@ -1700,7 +1700,7 @@
         <v>0.001574534197287968</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001394404881271137</v>
+        <v>0.001399130779191742</v>
       </c>
       <c r="K3" t="n">
         <v>0.0009582663578499515</v>
@@ -1751,7 +1751,7 @@
         <v>0.0003354981595551209</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000636738910066187</v>
+        <v>0.0006323102121033876</v>
       </c>
       <c r="AB3" t="n">
         <v>1.04329280829807e-05</v>
@@ -1766,7 +1766,7 @@
         <v>0.0002685560541366838</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0008394397607449169</v>
+        <v>-0.0008442428347122568</v>
       </c>
       <c r="AG3" t="n">
         <v>0.001372957231804978</v>
@@ -1781,7 +1781,7 @@
         <v>0.02808833709323328</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.05209603610739046</v>
+        <v>0.05209727065512806</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01250596745014503</v>
@@ -1829,7 +1829,7 @@
         <v>0.0001109231753630791</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.01081055343960391</v>
+        <v>0.01080586740399004</v>
       </c>
       <c r="BB3" t="n">
         <v>0.002261858660465164</v>
@@ -1856,7 +1856,7 @@
         <v>0.2326799035113259</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001809222882724295</v>
+        <v>0.001814442089404879</v>
       </c>
       <c r="BK3" t="n">
         <v>0.1301461665375512</v>
@@ -1868,7 +1868,7 @@
         <v>0.007373752542931144</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01080586740399004</v>
+        <v>0.01081055343960391</v>
       </c>
       <c r="BO3" t="n">
         <v>0.02331413313072963</v>
@@ -1892,19 +1892,19 @@
         <v>0.001465121564947487</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001209987713538007</v>
+        <v>0.001195843441967992</v>
       </c>
       <c r="BW3" t="n">
-        <v>-1.257846177874833e-05</v>
+        <v>-2.526043979388377e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001582278311454314</v>
+        <v>0.001591707825834323</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0005328083969018927</v>
+        <v>0.0005280891897286978</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0005280891897286978</v>
+        <v>0.0005233632918080924</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0009414698904789576</v>
@@ -1958,7 +1958,7 @@
         <v>0.06110190319465904</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.09730182341809851</v>
+        <v>0.09730650945371239</v>
       </c>
       <c r="CS3" t="n">
         <v>0.2558477808535205</v>
@@ -2024,10 +2024,10 @@
         <v>-0.0004174565772104067</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01004830969971754</v>
+        <v>0.0100435066257502</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.007108749021358775</v>
+        <v>0.007113468228531971</v>
       </c>
       <c r="DP3" t="n">
         <v>0.005918159979682566</v>
@@ -2111,7 +2111,7 @@
         <v>0.0005249446625467658</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01105177161142352</v>
+        <v>0.01105649081859672</v>
       </c>
       <c r="ER3" t="n">
         <v>0.0001036474855976488</v>
@@ -2154,7 +2154,7 @@
         <v>0.001993709884191137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002963599070709179</v>
+        <v>0.002958966732646381</v>
       </c>
       <c r="F4" t="n">
         <v>0.003662397928799421</v>
@@ -2169,7 +2169,7 @@
         <v>0.01065739525343982</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005229780631194291</v>
+        <v>0.00523452091503007</v>
       </c>
       <c r="K4" t="n">
         <v>0.002894519679431617</v>
@@ -2220,7 +2220,7 @@
         <v>0.001658829698930418</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002026657623515574</v>
+        <v>0.002026101355729119</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0009698307500806801</v>
@@ -2235,7 +2235,7 @@
         <v>0.001658789500295234</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004513514386147373</v>
+        <v>0.004504018722467995</v>
       </c>
       <c r="AG4" t="n">
         <v>0.001710342840175434</v>
@@ -2250,7 +2250,7 @@
         <v>0.01963388860368842</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02808573265506369</v>
+        <v>0.02809201664052876</v>
       </c>
       <c r="AL4" t="n">
         <v>0.02149284013596565</v>
@@ -2298,7 +2298,7 @@
         <v>0.003342692402604941</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.02445856498077541</v>
+        <v>0.02445977346330645</v>
       </c>
       <c r="BB4" t="n">
         <v>0.0114113037163639</v>
@@ -2325,7 +2325,7 @@
         <v>0.06357985697831871</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.009336226598216008</v>
+        <v>0.009338261791522749</v>
       </c>
       <c r="BK4" t="n">
         <v>0.08984910856775047</v>
@@ -2337,7 +2337,7 @@
         <v>0.02005956864355142</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.02445977346330645</v>
+        <v>0.02445856498077541</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02882831304244348</v>
@@ -2361,19 +2361,19 @@
         <v>0.01460152518218523</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.00379550875403113</v>
+        <v>0.003758039218442069</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001651048407075839</v>
+        <v>0.0001539622976712129</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01279427629033144</v>
+        <v>0.01278857398534746</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003903284258332893</v>
+        <v>0.003901428848579712</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003901428848579712</v>
+        <v>0.003913788673042979</v>
       </c>
       <c r="CA4" t="n">
         <v>0.008941463317135589</v>
@@ -2427,7 +2427,7 @@
         <v>0.04991720375888844</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.07886143789905438</v>
+        <v>0.07887019010005794</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1194033892533462</v>
@@ -2493,10 +2493,10 @@
         <v>0.003336114254897619</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.01883207402440181</v>
+        <v>0.01881954282382875</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01793688823110873</v>
+        <v>0.01794000327895921</v>
       </c>
       <c r="DP4" t="n">
         <v>0.03244337705018976</v>
@@ -2580,7 +2580,7 @@
         <v>0.001177861834550426</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.02326840238257302</v>
+        <v>0.02326793724358382</v>
       </c>
       <c r="ER4" t="n">
         <v>0.005739825224282238</v>
@@ -2833,7 +2833,7 @@
         <v>-0.004530438886267097</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0003674540682414684</v>
+        <v>-0.0003149606299212571</v>
       </c>
       <c r="BX5" t="n">
         <v>-0.02750472589792063</v>
@@ -2842,7 +2842,7 @@
         <v>-0.008648393194707027</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.008648393194707027</v>
+        <v>-0.008695652173913082</v>
       </c>
       <c r="CA5" t="n">
         <v>-0.0129436325678497</v>
@@ -3188,7 +3188,7 @@
         <v>0.0171999739890754</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03044334368466253</v>
+        <v>0.03037431469248581</v>
       </c>
       <c r="AL6" t="n">
         <v>-0.004993329342470184</v>
@@ -3657,7 +3657,7 @@
         <v>0.02666433562633578</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.05134804054380242</v>
+        <v>0.05140023261060826</v>
       </c>
       <c r="AL7" t="n">
         <v>0.0023479424553907</v>
@@ -3771,13 +3771,13 @@
         <v>0.0007526088642029194</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.220446049250313e-17</v>
+        <v>2.401536983671626e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>0.0007787582732140308</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002002872353155677</v>
+        <v>0.001979276317289702</v>
       </c>
       <c r="BZ7" t="n">
         <v>0.001979276317289702</v>
@@ -4045,7 +4045,7 @@
         <v>0.00613308509055655</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006539602522264876</v>
+        <v>0.006551417267066387</v>
       </c>
       <c r="K8" t="n">
         <v>0.0026433243237625</v>
@@ -4096,7 +4096,7 @@
         <v>0.001074909999506868</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001498471253409148</v>
+        <v>0.001487399508502149</v>
       </c>
       <c r="AB8" t="n">
         <v>0.000324711967432878</v>
@@ -4174,7 +4174,7 @@
         <v>-8.265303300502014e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00601714575791937</v>
+        <v>0.006005430668884692</v>
       </c>
       <c r="BB8" t="n">
         <v>0.004537435385273889</v>
@@ -4213,7 +4213,7 @@
         <v>0.00320100334624884</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.006005430668884692</v>
+        <v>0.00601714575791937</v>
       </c>
       <c r="BO8" t="n">
         <v>0.05046496097863767</v>
@@ -4372,7 +4372,7 @@
         <v>0.01609665828109381</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0154095090891205</v>
+        <v>0.01544490314291946</v>
       </c>
       <c r="DP8" t="n">
         <v>0.02930641095605625</v>
@@ -4456,7 +4456,7 @@
         <v>0.0001153582330665759</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.007529385111332056</v>
+        <v>0.007564779165131019</v>
       </c>
       <c r="ER8" t="n">
         <v>4.689888582841417e-05</v>
@@ -4580,7 +4580,7 @@
         <v>0.00447298494242695</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007204610951008683</v>
+        <v>0.007156580211335284</v>
       </c>
       <c r="AG9" t="n">
         <v>0.005516265912305462</v>
@@ -4706,7 +4706,7 @@
         <v>0.02980513728963685</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01027817067421024</v>
+        <v>0.01013672795851009</v>
       </c>
       <c r="BW9" t="n">
         <v>0.0001887682869277985</v>
@@ -4772,7 +4772,7 @@
         <v>0.165979381443299</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.2298500468603561</v>
+        <v>0.2298969072164948</v>
       </c>
       <c r="CS9" t="n">
         <v>0.3787422497785651</v>
@@ -4838,7 +4838,7 @@
         <v>0.005191127890514402</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.05427473583093184</v>
+        <v>0.05422670509125845</v>
       </c>
       <c r="DO9" t="n">
         <v>0.03940501043841334</v>
